--- a/untranslated/downloads/data-excel/6.3.1.xlsx
+++ b/untranslated/downloads/data-excel/6.3.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
@@ -351,7 +351,7 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -433,6 +433,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -730,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.42578125" style="12" customWidth="1"/>
@@ -740,7 +741,7 @@
     <col min="7" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="41.25" customHeight="1">
+    <row r="1" spans="1:18" ht="41.25" customHeight="1">
       <c r="A1" s="28" t="s">
         <v>39</v>
       </c>
@@ -759,7 +760,7 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75">
+    <row r="2" spans="1:18" ht="15.75">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -778,7 +779,7 @@
       <c r="J2" s="13"/>
       <c r="K2" s="11"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5" thickBot="1">
+    <row r="3" spans="1:18" ht="16.5" thickBot="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -796,8 +797,9 @@
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
+      <c r="R3" s="29"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,8 +851,11 @@
       <c r="Q4" s="4">
         <v>2023</v>
       </c>
+      <c r="R4" s="4">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" s="17" customFormat="1" ht="18" customHeight="1">
+    <row r="5" spans="1:18" s="17" customFormat="1" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
@@ -902,8 +907,11 @@
       <c r="Q5" s="10">
         <v>96.969944810665083</v>
       </c>
+      <c r="R5" s="10">
+        <v>97.8</v>
+      </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6" s="18" t="s">
         <v>9</v>
       </c>
@@ -955,8 +963,11 @@
       <c r="Q6" s="24">
         <v>96.173557859042035</v>
       </c>
+      <c r="R6" s="25">
+        <v>93.8</v>
+      </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7" s="20" t="s">
         <v>13</v>
       </c>
@@ -1008,8 +1019,11 @@
       <c r="Q7" s="25">
         <v>62.289845326160055</v>
       </c>
+      <c r="R7" s="25">
+        <v>62.3</v>
+      </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8" s="20" t="s">
         <v>16</v>
       </c>
@@ -1061,8 +1075,11 @@
       <c r="Q8" s="25">
         <v>100</v>
       </c>
+      <c r="R8" s="25">
+        <v>100</v>
+      </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9" s="20" t="s">
         <v>19</v>
       </c>
@@ -1114,8 +1131,11 @@
       <c r="Q9" s="25">
         <v>100</v>
       </c>
+      <c r="R9" s="25">
+        <v>100</v>
+      </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" s="20" t="s">
         <v>22</v>
       </c>
@@ -1167,8 +1187,11 @@
       <c r="Q10" s="26" t="s">
         <v>12</v>
       </c>
+      <c r="R10" s="26" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
@@ -1220,8 +1243,11 @@
       <c r="Q11" s="25">
         <v>100</v>
       </c>
+      <c r="R11" s="25">
+        <v>100</v>
+      </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12" s="20" t="s">
         <v>28</v>
       </c>
@@ -1273,8 +1299,11 @@
       <c r="Q12" s="25">
         <v>58.090784503861151</v>
       </c>
+      <c r="R12" s="25">
+        <v>80.900000000000006</v>
+      </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" s="20" t="s">
         <v>31</v>
       </c>
@@ -1326,8 +1355,11 @@
       <c r="Q13" s="25">
         <v>100</v>
       </c>
+      <c r="R13" s="25">
+        <v>100</v>
+      </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1">
       <c r="A14" s="22" t="s">
         <v>34</v>
       </c>
@@ -1377,6 +1409,9 @@
         <v>100</v>
       </c>
       <c r="Q14" s="27">
+        <v>100</v>
+      </c>
+      <c r="R14" s="27">
         <v>100</v>
       </c>
     </row>
